--- a/Result/profitability/2439.xlsx
+++ b/Result/profitability/2439.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>1.55</v>
+        <v>1.28875</v>
       </c>
       <c r="N2" t="n">
-        <v>13.08875</v>
+        <v>12.65</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.36375</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>13.8725</v>
+        <v>13.3875</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1.21375</v>
+        <v>1.09875</v>
       </c>
       <c r="N4" t="n">
-        <v>14.66875</v>
+        <v>14.37125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0675</v>
+        <v>1.12875</v>
       </c>
       <c r="N5" t="n">
-        <v>15.3875</v>
+        <v>15.17125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07125</v>
+        <v>0.8424999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>15.91125</v>
+        <v>15.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8175</v>
+        <v>0.68</v>
       </c>
       <c r="N7" t="n">
-        <v>16.94125</v>
+        <v>16.735</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7987500000000001</v>
+        <v>0.7324999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>18.66875</v>
+        <v>18.4375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10438</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9396</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1042</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>158</v>
+      </c>
+      <c r="J75" t="n">
+        <v>162</v>
+      </c>
+      <c r="K75" t="n">
+        <v>124</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.54125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.19625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5145631067961165</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1563820794590025</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.147736976942784</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
